--- a/data/trans_bre/P26-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P26-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,27</t>
+          <t>4,33; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 15,46</t>
+          <t>4,68; 15,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,07</t>
+          <t>-3,42; 6,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,75</t>
+          <t>-3,34; 3,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,19; 54,17</t>
+          <t>13,69; 55,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,26; 62,42</t>
+          <t>14,79; 61,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 32,11</t>
+          <t>-12,25; 29,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 58,31</t>
+          <t>-29,14; 54,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,18</t>
+          <t>4,53; 13,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 11,68</t>
+          <t>2,61; 11,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,51</t>
+          <t>-2,4; 5,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 6,01</t>
+          <t>-54,59; 6,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 50,08</t>
+          <t>15,13; 53,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 38,94</t>
+          <t>7,51; 38,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 25,14</t>
+          <t>-9,71; 25,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,1; 70,11</t>
+          <t>-80,74; 69,98</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 11,2</t>
+          <t>0,48; 11,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 13,84</t>
+          <t>2,88; 13,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,5</t>
+          <t>1,87; 11,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 5,96</t>
+          <t>-7,69; 6,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 40,43</t>
+          <t>1,59; 41,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 44,86</t>
+          <t>7,63; 44,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 44,79</t>
+          <t>6,21; 47,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 54,57</t>
+          <t>-51,3; 57,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,43</t>
+          <t>4,62; 13,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,02</t>
+          <t>-5,38; 3,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,69</t>
+          <t>-6,99; 1,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,46</t>
+          <t>-5,83; 2,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 51,99</t>
+          <t>16,12; 52,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 11,76</t>
+          <t>-13,63; 10,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 7,81</t>
+          <t>-26,19; 5,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 18,13</t>
+          <t>-31,53; 15,85</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,12</t>
+          <t>6,25; 10,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,21</t>
+          <t>3,48; 8,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,66</t>
+          <t>-0,67; 3,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 1,91</t>
+          <t>-28,66; 1,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 40,75</t>
+          <t>20,94; 39,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,83; 25,92</t>
+          <t>10,03; 26,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 15,11</t>
+          <t>-2,56; 15,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 16,58</t>
+          <t>-72,31; 16,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P26-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P26-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 14,11</t>
+          <t>4,03; 14,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 15,84</t>
+          <t>4,55; 15,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,67</t>
+          <t>-3,51; 6,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,71</t>
+          <t>-3,23; 3,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 55,73</t>
+          <t>12,66; 57,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,79; 61,88</t>
+          <t>14,4; 59,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 29,39</t>
+          <t>-12,18; 29,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 54,7</t>
+          <t>-28,59; 54,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-14,84</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-50,87%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 13,89</t>
+          <t>4,35; 13,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 11,83</t>
+          <t>2,9; 11,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,5</t>
+          <t>-2,39; 5,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 6,08</t>
+          <t>1,66; 7,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 53,7</t>
+          <t>14,14; 51,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 38,78</t>
+          <t>8,41; 38,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 25,76</t>
+          <t>-9,08; 26,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,74; 69,98</t>
+          <t>14,22; 102,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 11,14</t>
+          <t>0,71; 11,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 13,71</t>
+          <t>3,0; 13,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 11,59</t>
+          <t>1,83; 11,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,22</t>
+          <t>0,64; 8,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 41,04</t>
+          <t>1,9; 42,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 44,78</t>
+          <t>8,29; 44,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 47,29</t>
+          <t>5,78; 42,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 57,76</t>
+          <t>4,73; 93,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,56%</t>
+          <t>-5,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,43</t>
+          <t>4,59; 12,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 3,47</t>
+          <t>-5,28; 4,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 1,32</t>
+          <t>-6,69; 1,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 2,2</t>
+          <t>-4,29; 2,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 52,11</t>
+          <t>15,32; 50,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 10,04</t>
+          <t>-13,38; 13,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 5,88</t>
+          <t>-24,91; 6,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 15,85</t>
+          <t>-23,68; 22,36</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-30,36%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,93</t>
+          <t>6,1; 11,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,32</t>
+          <t>3,44; 8,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,75</t>
+          <t>-0,47; 3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 1,85</t>
+          <t>0,46; 3,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,94; 39,62</t>
+          <t>20,41; 39,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 26,19</t>
+          <t>10,35; 26,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 15,44</t>
+          <t>-2,04; 15,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 16,22</t>
+          <t>3,67; 36,2</t>
         </is>
       </c>
     </row>
